--- a/excell/avtoil_database.xlsx
+++ b/excell/avtoil_database.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FEA450-8107-42CF-84F7-441D61E5BA0E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE14226F-7657-455B-96C5-9B19463DE228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="938" firstSheet="5" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Engine oil - PC" sheetId="1" r:id="rId1"/>
@@ -5556,7 +5556,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5602,13 +5602,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -5950,7 +5943,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6003,23 +5996,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6036,22 +6023,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6073,27 +6051,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6109,21 +6066,43 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6138,9 +6117,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6152,7 +6128,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6192,46 +6170,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6681,63 +6629,63 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="63" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65" t="s">
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="63" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="97" t="s">
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="H3" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="97" t="s">
+      <c r="I3" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="97" t="s">
+      <c r="J3" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="97" t="s">
+      <c r="K3" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="98"/>
+      <c r="L3" s="64"/>
     </row>
     <row r="4" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>322</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="39" t="s">
         <v>1438</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -6769,7 +6717,7 @@
       <c r="B5" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>323</v>
       </c>
       <c r="D5" s="7" t="s">
@@ -6804,7 +6752,7 @@
       <c r="B6" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>324</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -6839,7 +6787,7 @@
       <c r="B7" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>325</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -6874,7 +6822,7 @@
       <c r="B8" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>326</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -6909,7 +6857,7 @@
       <c r="B9" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>327</v>
       </c>
       <c r="D9" s="7" t="s">
@@ -6944,7 +6892,7 @@
       <c r="B10" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="44" t="s">
         <v>328</v>
       </c>
       <c r="D10" s="7" t="s">
@@ -6979,7 +6927,7 @@
       <c r="B11" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="44" t="s">
         <v>329</v>
       </c>
       <c r="D11" s="7" t="s">
@@ -7014,7 +6962,7 @@
       <c r="B12" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="44" t="s">
         <v>330</v>
       </c>
       <c r="D12" s="7" t="s">
@@ -7049,7 +6997,7 @@
       <c r="B13" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="44" t="s">
         <v>331</v>
       </c>
       <c r="D13" s="7" t="s">
@@ -7084,7 +7032,7 @@
       <c r="B14" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="44" t="s">
         <v>332</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -7119,7 +7067,7 @@
       <c r="B15" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="44" t="s">
         <v>333</v>
       </c>
       <c r="D15" s="7" t="s">
@@ -7154,7 +7102,7 @@
       <c r="B16" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="44" t="s">
         <v>334</v>
       </c>
       <c r="D16" s="7" t="s">
@@ -7189,10 +7137,10 @@
       <c r="B17" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="44" t="s">
         <v>335</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="39" t="s">
         <v>508</v>
       </c>
       <c r="E17" s="7" t="s">
@@ -7224,10 +7172,10 @@
       <c r="B18" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="44" t="s">
         <v>336</v>
       </c>
-      <c r="D18" s="57" t="s">
+      <c r="D18" s="39" t="s">
         <v>506</v>
       </c>
       <c r="E18" s="7" t="s">
@@ -7259,10 +7207,10 @@
       <c r="B19" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="D19" s="57" t="s">
+      <c r="D19" s="39" t="s">
         <v>504</v>
       </c>
       <c r="E19" s="7" t="s">
@@ -7294,7 +7242,7 @@
       <c r="B20" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="44" t="s">
         <v>338</v>
       </c>
       <c r="D20" s="7" t="s">
@@ -7329,7 +7277,7 @@
       <c r="B21" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="44" t="s">
         <v>339</v>
       </c>
       <c r="D21" s="7" t="s">
@@ -7364,7 +7312,7 @@
       <c r="B22" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="44" t="s">
         <v>340</v>
       </c>
       <c r="D22" s="7" t="s">
@@ -7399,7 +7347,7 @@
       <c r="B23" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="44" t="s">
         <v>341</v>
       </c>
       <c r="D23" s="7" t="s">
@@ -7434,7 +7382,7 @@
       <c r="B24" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="44" t="s">
         <v>340</v>
       </c>
       <c r="D24" s="7" t="s">
@@ -7469,7 +7417,7 @@
       <c r="B25" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="44" t="s">
         <v>342</v>
       </c>
       <c r="D25" s="7" t="s">
@@ -7504,7 +7452,7 @@
       <c r="B26" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="44" t="s">
         <v>343</v>
       </c>
       <c r="D26" s="7" t="s">
@@ -7539,7 +7487,7 @@
       <c r="B27" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="44" t="s">
         <v>344</v>
       </c>
       <c r="D27" s="7" t="s">
@@ -7574,7 +7522,7 @@
       <c r="B28" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="44" t="s">
         <v>345</v>
       </c>
       <c r="D28" s="7" t="s">
@@ -7609,7 +7557,7 @@
       <c r="B29" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" s="44" t="s">
         <v>346</v>
       </c>
       <c r="D29" s="7" t="s">
@@ -7644,7 +7592,7 @@
       <c r="B30" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" s="44" t="s">
         <v>347</v>
       </c>
       <c r="D30" s="7" t="s">
@@ -7679,7 +7627,7 @@
       <c r="B31" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C31" s="58" t="s">
+      <c r="C31" s="44" t="s">
         <v>348</v>
       </c>
       <c r="D31" s="7" t="s">
@@ -7714,7 +7662,7 @@
       <c r="B32" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C32" s="58" t="s">
+      <c r="C32" s="44" t="s">
         <v>349</v>
       </c>
       <c r="D32" s="7" t="s">
@@ -7749,7 +7697,7 @@
       <c r="B33" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C33" s="58" t="s">
+      <c r="C33" s="44" t="s">
         <v>350</v>
       </c>
       <c r="D33" s="7" t="s">
@@ -7784,7 +7732,7 @@
       <c r="B34" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" s="44" t="s">
         <v>351</v>
       </c>
       <c r="D34" s="7" t="s">
@@ -7819,7 +7767,7 @@
       <c r="B35" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="44" t="s">
         <v>352</v>
       </c>
       <c r="D35" s="7" t="s">
@@ -7854,7 +7802,7 @@
       <c r="B36" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C36" s="58" t="s">
+      <c r="C36" s="44" t="s">
         <v>353</v>
       </c>
       <c r="D36" s="7" t="s">
@@ -7889,7 +7837,7 @@
       <c r="B37" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C37" s="58" t="s">
+      <c r="C37" s="44" t="s">
         <v>354</v>
       </c>
       <c r="D37" s="7" t="s">
@@ -7924,7 +7872,7 @@
       <c r="B38" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C38" s="58" t="s">
+      <c r="C38" s="44" t="s">
         <v>355</v>
       </c>
       <c r="D38" s="7" t="s">
@@ -7959,7 +7907,7 @@
       <c r="B39" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" s="44" t="s">
         <v>356</v>
       </c>
       <c r="D39" s="7" t="s">
@@ -7994,7 +7942,7 @@
       <c r="B40" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C40" s="58" t="s">
+      <c r="C40" s="44" t="s">
         <v>357</v>
       </c>
       <c r="D40" s="7" t="s">
@@ -8029,7 +7977,7 @@
       <c r="B41" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" s="44" t="s">
         <v>358</v>
       </c>
       <c r="D41" s="7" t="s">
@@ -8064,7 +8012,7 @@
       <c r="B42" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="C42" s="58" t="s">
+      <c r="C42" s="44" t="s">
         <v>359</v>
       </c>
       <c r="D42" s="7" t="s">
@@ -8099,7 +8047,7 @@
       <c r="B43" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="44" t="s">
         <v>360</v>
       </c>
       <c r="D43" s="7" t="s">
@@ -8134,7 +8082,7 @@
       <c r="B44" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C44" s="58" t="s">
+      <c r="C44" s="44" t="s">
         <v>361</v>
       </c>
       <c r="D44" s="7" t="s">
@@ -8169,7 +8117,7 @@
       <c r="B45" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C45" s="58" t="s">
+      <c r="C45" s="44" t="s">
         <v>362</v>
       </c>
       <c r="D45" s="7" t="s">
@@ -8204,7 +8152,7 @@
       <c r="B46" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="C46" s="58" t="s">
+      <c r="C46" s="44" t="s">
         <v>363</v>
       </c>
       <c r="D46" s="7" t="s">
@@ -8239,7 +8187,7 @@
       <c r="B47" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C47" s="58" t="s">
+      <c r="C47" s="44" t="s">
         <v>364</v>
       </c>
       <c r="D47" s="7" t="s">
@@ -8274,7 +8222,7 @@
       <c r="B48" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C48" s="58" t="s">
+      <c r="C48" s="44" t="s">
         <v>365</v>
       </c>
       <c r="D48" s="7" t="s">
@@ -8309,7 +8257,7 @@
       <c r="B49" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C49" s="58" t="s">
+      <c r="C49" s="44" t="s">
         <v>366</v>
       </c>
       <c r="D49" s="7" t="s">
@@ -8344,7 +8292,7 @@
       <c r="B50" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="44" t="s">
         <v>367</v>
       </c>
       <c r="D50" s="7" t="s">
@@ -8379,7 +8327,7 @@
       <c r="B51" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="44" t="s">
         <v>368</v>
       </c>
       <c r="D51" s="7" t="s">
@@ -8412,11 +8360,11 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="L2:L3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:L3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
   </mergeCells>
@@ -8446,10 +8394,10 @@
       <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
       <c r="G2" s="17" t="s">
@@ -8460,7 +8408,7 @@
       <c r="B3" s="4" t="s">
         <v>937</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="44" t="s">
         <v>934</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -8480,7 +8428,7 @@
       <c r="B4" s="4" t="s">
         <v>938</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>935</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -8500,7 +8448,7 @@
       <c r="B5" s="4" t="s">
         <v>939</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>936</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -8539,33 +8487,33 @@
       <c r="C2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="25" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="22" t="s">
         <v>946</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="44" t="s">
         <v>953</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="23" t="s">
         <v>961</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="23" t="s">
         <v>960</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="23" t="s">
         <v>962</v>
       </c>
       <c r="G3" s="19" t="s">
@@ -8573,19 +8521,19 @@
       </c>
     </row>
     <row r="4" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="22" t="s">
         <v>947</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>954</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="23" t="s">
         <v>969</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="23" t="s">
         <v>960</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="23" t="s">
         <v>968</v>
       </c>
       <c r="G4" s="19" t="s">
@@ -8593,19 +8541,19 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="22" t="s">
         <v>948</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>955</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="23" t="s">
         <v>970</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="23" t="s">
         <v>960</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="23" t="s">
         <v>967</v>
       </c>
       <c r="G5" s="19" t="s">
@@ -8613,19 +8561,19 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>949</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>956</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="23" t="s">
         <v>971</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="23" t="s">
         <v>960</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="23" t="s">
         <v>966</v>
       </c>
       <c r="G6" s="19" t="s">
@@ -8633,19 +8581,19 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="22" t="s">
         <v>950</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>957</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="23" t="s">
         <v>972</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="23" t="s">
         <v>960</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="23" t="s">
         <v>965</v>
       </c>
       <c r="G7" s="19" t="s">
@@ -8653,19 +8601,19 @@
       </c>
     </row>
     <row r="8" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="22" t="s">
         <v>951</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>958</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="23" t="s">
         <v>973</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="23" t="s">
         <v>960</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="23" t="s">
         <v>964</v>
       </c>
       <c r="G8" s="19" t="s">
@@ -8673,19 +8621,19 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="22" t="s">
         <v>952</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>959</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="23" t="s">
         <v>974</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="23" t="s">
         <v>960</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="23" t="s">
         <v>963</v>
       </c>
       <c r="G9" s="19" t="s">
@@ -8719,13 +8667,13 @@
       <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="25" t="s">
         <v>3</v>
       </c>
     </row>
@@ -8733,7 +8681,7 @@
       <c r="B3" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="44" t="s">
         <v>981</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -8753,7 +8701,7 @@
       <c r="B4" s="4" t="s">
         <v>976</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>982</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -8773,7 +8721,7 @@
       <c r="B5" s="4" t="s">
         <v>977</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>983</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -8793,7 +8741,7 @@
       <c r="B6" s="4" t="s">
         <v>978</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>984</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -8813,7 +8761,7 @@
       <c r="B7" s="4" t="s">
         <v>979</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>985</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -8839,7 +8787,7 @@
   <dimension ref="B2:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.42578125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="26" customWidth="1"/>
     <col min="3" max="3" width="34.28515625" customWidth="1"/>
     <col min="4" max="4" width="59.5703125" customWidth="1"/>
     <col min="5" max="5" width="41.7109375" customWidth="1"/>
@@ -8857,10 +8805,10 @@
       <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
       <c r="G2" s="17" t="s">
@@ -8871,7 +8819,7 @@
       <c r="B3" s="4" t="s">
         <v>1003</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="44" t="s">
         <v>996</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -8891,7 +8839,7 @@
       <c r="B4" s="4" t="s">
         <v>1004</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>997</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -8911,7 +8859,7 @@
       <c r="B5" s="4" t="s">
         <v>1005</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>998</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -8931,7 +8879,7 @@
       <c r="B6" s="4" t="s">
         <v>1006</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>999</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -8951,7 +8899,7 @@
       <c r="B7" s="4" t="s">
         <v>1007</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>1000</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -8971,7 +8919,7 @@
       <c r="B8" s="4" t="s">
         <v>1008</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>1001</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -8991,7 +8939,7 @@
       <c r="B9" s="5" t="s">
         <v>1009</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>1002</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -9035,10 +8983,10 @@
       <c r="D2" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
       <c r="G2" s="17" t="s">
@@ -9049,160 +8997,160 @@
       </c>
     </row>
     <row r="3" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="22" t="s">
         <v>891</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="23" t="s">
         <v>1088</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="23" t="s">
         <v>1031</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="23" t="s">
         <v>1072</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <v>30</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="22" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="22" t="s">
         <v>892</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="23" t="s">
         <v>1089</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="23" t="s">
         <v>1032</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="23" t="s">
         <v>1073</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <v>30</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="22" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="22" t="s">
         <v>893</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="23" t="s">
         <v>1090</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="23" t="s">
         <v>1033</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="23" t="s">
         <v>1034</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <v>40</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="22" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>894</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="23" t="s">
         <v>1091</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="23" t="s">
         <v>1035</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="23" t="s">
         <v>1074</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <v>50</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="22" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="22" t="s">
         <v>895</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="23" t="s">
         <v>1092</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="23" t="s">
         <v>1036</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="23" t="s">
         <v>1075</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="22">
         <v>40</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="22" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="22" t="s">
         <v>896</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="23" t="s">
         <v>1093</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="23" t="s">
         <v>1037</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="23" t="s">
         <v>1076</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <v>20</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="22" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="22" t="s">
         <v>897</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="23" t="s">
         <v>1094</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="23" t="s">
         <v>1038</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="23" t="s">
         <v>1077</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="22" t="s">
         <v>198</v>
       </c>
       <c r="H9" s="19" t="s">
@@ -9210,22 +9158,22 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="22" t="s">
         <v>898</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="23" t="s">
         <v>1095</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="23" t="s">
         <v>1039</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="23" t="s">
         <v>1040</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <v>90</v>
       </c>
       <c r="H10" s="19" t="s">
@@ -9233,22 +9181,22 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="22" t="s">
         <v>899</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="23" t="s">
         <v>1096</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="23" t="s">
         <v>1041</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="23" t="s">
         <v>1078</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="22">
         <v>90</v>
       </c>
       <c r="H11" s="19" t="s">
@@ -9256,19 +9204,19 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="22" t="s">
         <v>900</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="23" t="s">
         <v>1097</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="23" t="s">
         <v>1042</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="23" t="s">
         <v>1079</v>
       </c>
       <c r="G12" s="19">
@@ -9279,42 +9227,42 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="22" t="s">
         <v>901</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="27" t="s">
         <v>1098</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="27" t="s">
         <v>1043</v>
       </c>
-      <c r="F13" s="30" t="s">
+      <c r="F13" s="27" t="s">
         <v>1080</v>
       </c>
       <c r="G13" s="2">
         <v>46</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H13" s="28" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="22" t="s">
         <v>902</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="23" t="s">
         <v>1099</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="23" t="s">
         <v>1044</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="23" t="s">
         <v>1081</v>
       </c>
       <c r="G14" s="19" t="s">
@@ -9325,45 +9273,45 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="22" t="s">
         <v>903</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="23" t="s">
         <v>1100</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="23" t="s">
         <v>1045</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="23" t="s">
         <v>1046</v>
       </c>
-      <c r="G15" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="33" t="s">
+      <c r="G15" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="29" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="22" t="s">
         <v>904</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="23" t="s">
         <v>1101</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="23" t="s">
         <v>1047</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="23" t="s">
         <v>1082</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <v>40</v>
       </c>
       <c r="H16" s="19" t="s">
@@ -9371,19 +9319,19 @@
       </c>
     </row>
     <row r="17" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="22" t="s">
         <v>1025</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="23" t="s">
         <v>1102</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="23" t="s">
         <v>1048</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="23" t="s">
         <v>1083</v>
       </c>
       <c r="G17" s="19" t="s">
@@ -9394,19 +9342,19 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="22" t="s">
         <v>1026</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="22" t="s">
         <v>1067</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="23" t="s">
         <v>1103</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="23" t="s">
         <v>1048</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="23" t="s">
         <v>1084</v>
       </c>
       <c r="G18" s="19" t="s">
@@ -9417,19 +9365,19 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="22" t="s">
         <v>1027</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="22" t="s">
         <v>1068</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="23" t="s">
         <v>1104</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="23" t="s">
         <v>1048</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="F19" s="23" t="s">
         <v>1085</v>
       </c>
       <c r="G19" s="19" t="s">
@@ -9440,19 +9388,19 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="22" t="s">
         <v>1028</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="22" t="s">
         <v>1069</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="23" t="s">
         <v>1105</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="23" t="s">
         <v>1048</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F20" s="23" t="s">
         <v>1086</v>
       </c>
       <c r="G20" s="19" t="s">
@@ -9463,19 +9411,19 @@
       </c>
     </row>
     <row r="21" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="22" t="s">
         <v>1029</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="22" t="s">
         <v>1070</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="23" t="s">
         <v>1106</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="23" t="s">
         <v>1049</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="23" t="s">
         <v>1050</v>
       </c>
       <c r="G21" s="19" t="s">
@@ -9486,19 +9434,19 @@
       </c>
     </row>
     <row r="22" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="22" t="s">
         <v>1030</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="22" t="s">
         <v>1071</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="23" t="s">
         <v>1107</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="23" t="s">
         <v>1051</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="23" t="s">
         <v>1087</v>
       </c>
       <c r="G22" s="19" t="s">
@@ -9537,52 +9485,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="E2" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="81" t="s">
+      <c r="G2" s="76" t="s">
         <v>208</v>
       </c>
-      <c r="H2" s="65" t="s">
+      <c r="H2" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="68" t="s">
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="63" t="s">
         <v>210</v>
       </c>
-      <c r="O2" s="68" t="s">
+      <c r="O2" s="63" t="s">
         <v>211</v>
       </c>
-      <c r="P2" s="68" t="s">
+      <c r="P2" s="63" t="s">
         <v>212</v>
       </c>
-      <c r="Q2" s="68" t="s">
+      <c r="Q2" s="63" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="79"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="82"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="77"/>
       <c r="H3" s="1" t="s">
         <v>214</v>
       </c>
@@ -9601,98 +9549,98 @@
       <c r="M3" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="69"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
     </row>
     <row r="4" spans="2:17" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="22" t="s">
         <v>1108</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="23" t="s">
         <v>1112</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="23" t="s">
         <v>1110</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="I4" s="37"/>
-      <c r="J4" s="24" t="s">
+      <c r="I4" s="32"/>
+      <c r="J4" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L4" s="38" t="s">
+      <c r="L4" s="33" t="s">
         <v>226</v>
       </c>
-      <c r="M4" s="37"/>
-      <c r="N4" s="24" t="s">
+      <c r="M4" s="32"/>
+      <c r="N4" s="22" t="s">
         <v>227</v>
       </c>
       <c r="O4" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="P4" s="39" t="s">
+      <c r="P4" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="Q4" s="40"/>
+      <c r="Q4" s="35"/>
     </row>
     <row r="5" spans="2:17" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="22" t="s">
         <v>1109</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="23" t="s">
         <v>1113</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="23" t="s">
         <v>1111</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24" t="s">
+      <c r="I5" s="22"/>
+      <c r="J5" s="22" t="s">
         <v>224</v>
       </c>
       <c r="K5" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="M5" s="25"/>
-      <c r="N5" s="24" t="s">
+      <c r="M5" s="23"/>
+      <c r="N5" s="22" t="s">
         <v>227</v>
       </c>
       <c r="O5" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="P5" s="39" t="s">
+      <c r="P5" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="Q5" s="41"/>
+      <c r="Q5" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -9727,22 +9675,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
     </row>
@@ -9750,7 +9698,7 @@
       <c r="B3" s="4" t="s">
         <v>1129</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="44" t="s">
         <v>1171</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -9770,7 +9718,7 @@
       <c r="B4" s="4" t="s">
         <v>1130</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>1172</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -9790,7 +9738,7 @@
       <c r="B5" s="4" t="s">
         <v>1131</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>1173</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -9810,7 +9758,7 @@
       <c r="B6" s="4" t="s">
         <v>1132</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>1174</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -9830,7 +9778,7 @@
       <c r="B7" s="4" t="s">
         <v>1133</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>1175</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -9850,7 +9798,7 @@
       <c r="B8" s="4" t="s">
         <v>1134</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>1176</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -9870,7 +9818,7 @@
       <c r="B9" s="4" t="s">
         <v>1135</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>1177</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -9890,7 +9838,7 @@
       <c r="B10" s="4" t="s">
         <v>1136</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="44" t="s">
         <v>1178</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -9910,7 +9858,7 @@
       <c r="B11" s="4" t="s">
         <v>1137</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="44" t="s">
         <v>1179</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -9930,7 +9878,7 @@
       <c r="B12" s="4" t="s">
         <v>1138</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="44" t="s">
         <v>1180</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -9950,7 +9898,7 @@
       <c r="B13" s="4" t="s">
         <v>1139</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="44" t="s">
         <v>1181</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -9970,7 +9918,7 @@
       <c r="B14" s="4" t="s">
         <v>1140</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="44" t="s">
         <v>1182</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -9990,7 +9938,7 @@
       <c r="B15" s="4" t="s">
         <v>1141</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="44" t="s">
         <v>1183</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -10010,7 +9958,7 @@
       <c r="B16" s="4" t="s">
         <v>1142</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="44" t="s">
         <v>1184</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -10030,7 +9978,7 @@
       <c r="B17" s="4" t="s">
         <v>1143</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="44" t="s">
         <v>1185</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -10050,7 +9998,7 @@
       <c r="B18" s="4" t="s">
         <v>1144</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="44" t="s">
         <v>1186</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -10070,7 +10018,7 @@
       <c r="B19" s="4" t="s">
         <v>1145</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="44" t="s">
         <v>1187</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -10090,7 +10038,7 @@
       <c r="B20" s="4" t="s">
         <v>1146</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="44" t="s">
         <v>1188</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -10110,7 +10058,7 @@
       <c r="B21" s="4" t="s">
         <v>1147</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="44" t="s">
         <v>1189</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -10130,7 +10078,7 @@
       <c r="B22" s="4" t="s">
         <v>1148</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="44" t="s">
         <v>1190</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -10150,7 +10098,7 @@
       <c r="B23" s="4" t="s">
         <v>1149</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="44" t="s">
         <v>1191</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -10170,7 +10118,7 @@
       <c r="B24" s="4" t="s">
         <v>1150</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="44" t="s">
         <v>1192</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -10190,7 +10138,7 @@
       <c r="B25" s="4" t="s">
         <v>1151</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="44" t="s">
         <v>1193</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -10210,7 +10158,7 @@
       <c r="B26" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="44" t="s">
         <v>1194</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -10230,7 +10178,7 @@
       <c r="B27" s="4" t="s">
         <v>1153</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="44" t="s">
         <v>1195</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -10250,7 +10198,7 @@
       <c r="B28" s="4" t="s">
         <v>1154</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="44" t="s">
         <v>1196</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -10270,7 +10218,7 @@
       <c r="B29" s="4" t="s">
         <v>1155</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" s="44" t="s">
         <v>1197</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -10290,7 +10238,7 @@
       <c r="B30" s="4" t="s">
         <v>1156</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" s="44" t="s">
         <v>1198</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -10310,7 +10258,7 @@
       <c r="B31" s="4" t="s">
         <v>1157</v>
       </c>
-      <c r="C31" s="58" t="s">
+      <c r="C31" s="44" t="s">
         <v>1199</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -10330,7 +10278,7 @@
       <c r="B32" s="4" t="s">
         <v>1158</v>
       </c>
-      <c r="C32" s="58" t="s">
+      <c r="C32" s="44" t="s">
         <v>1200</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -10350,7 +10298,7 @@
       <c r="B33" s="4" t="s">
         <v>1159</v>
       </c>
-      <c r="C33" s="58" t="s">
+      <c r="C33" s="44" t="s">
         <v>1201</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -10370,7 +10318,7 @@
       <c r="B34" s="4" t="s">
         <v>1160</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" s="44" t="s">
         <v>1202</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -10390,7 +10338,7 @@
       <c r="B35" s="4" t="s">
         <v>1161</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="44" t="s">
         <v>1203</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -10410,7 +10358,7 @@
       <c r="B36" s="4" t="s">
         <v>1162</v>
       </c>
-      <c r="C36" s="58" t="s">
+      <c r="C36" s="44" t="s">
         <v>1204</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -10430,7 +10378,7 @@
       <c r="B37" s="4" t="s">
         <v>1163</v>
       </c>
-      <c r="C37" s="58" t="s">
+      <c r="C37" s="44" t="s">
         <v>1205</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -10450,7 +10398,7 @@
       <c r="B38" s="4" t="s">
         <v>1164</v>
       </c>
-      <c r="C38" s="58" t="s">
+      <c r="C38" s="44" t="s">
         <v>1206</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -10470,7 +10418,7 @@
       <c r="B39" s="4" t="s">
         <v>1165</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" s="44" t="s">
         <v>1207</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -10482,7 +10430,7 @@
       <c r="F39" s="3" t="s">
         <v>1256</v>
       </c>
-      <c r="G39" s="44" t="s">
+      <c r="G39" s="29" t="s">
         <v>260</v>
       </c>
     </row>
@@ -10490,7 +10438,7 @@
       <c r="B40" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C40" s="58" t="s">
+      <c r="C40" s="44" t="s">
         <v>1208</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -10502,7 +10450,7 @@
       <c r="F40" s="3" t="s">
         <v>1260</v>
       </c>
-      <c r="G40" s="44" t="s">
+      <c r="G40" s="29" t="s">
         <v>260</v>
       </c>
     </row>
@@ -10510,7 +10458,7 @@
       <c r="B41" s="4" t="s">
         <v>1167</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" s="44" t="s">
         <v>1209</v>
       </c>
       <c r="D41" s="3" t="s">
@@ -10522,7 +10470,7 @@
       <c r="F41" s="3" t="s">
         <v>1259</v>
       </c>
-      <c r="G41" s="44" t="s">
+      <c r="G41" s="29" t="s">
         <v>260</v>
       </c>
     </row>
@@ -10530,7 +10478,7 @@
       <c r="B42" s="4" t="s">
         <v>1168</v>
       </c>
-      <c r="C42" s="58" t="s">
+      <c r="C42" s="44" t="s">
         <v>1210</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -10542,7 +10490,7 @@
       <c r="F42" s="3" t="s">
         <v>1258</v>
       </c>
-      <c r="G42" s="44" t="s">
+      <c r="G42" s="29" t="s">
         <v>260</v>
       </c>
     </row>
@@ -10550,7 +10498,7 @@
       <c r="B43" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="44" t="s">
         <v>1211</v>
       </c>
       <c r="D43" s="3" t="s">
@@ -10562,7 +10510,7 @@
       <c r="F43" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="G43" s="44" t="s">
+      <c r="G43" s="29" t="s">
         <v>260</v>
       </c>
     </row>
@@ -10570,7 +10518,7 @@
       <c r="B44" s="4" t="s">
         <v>1170</v>
       </c>
-      <c r="C44" s="58" t="s">
+      <c r="C44" s="44" t="s">
         <v>1212</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -10606,30 +10554,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="18" t="s">
         <v>1269</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="44" t="s">
         <v>1282</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -10641,15 +10589,15 @@
       <c r="F3" s="3" t="s">
         <v>1266</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="38" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="18" t="s">
         <v>1270</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>1283</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -10661,15 +10609,15 @@
       <c r="F4" s="3" t="s">
         <v>1266</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="38" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>1271</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>1284</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -10681,15 +10629,15 @@
       <c r="F5" s="3" t="s">
         <v>1266</v>
       </c>
-      <c r="G5" s="50" t="s">
+      <c r="G5" s="38" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="18" t="s">
         <v>1272</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>1285</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -10701,15 +10649,15 @@
       <c r="F6" s="3" t="s">
         <v>1266</v>
       </c>
-      <c r="G6" s="50" t="s">
+      <c r="G6" s="38" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="18" t="s">
         <v>1273</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>1286</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -10721,15 +10669,15 @@
       <c r="F7" s="3" t="s">
         <v>1266</v>
       </c>
-      <c r="G7" s="50" t="s">
+      <c r="G7" s="38" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="18" t="s">
         <v>1274</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>1287</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -10741,15 +10689,15 @@
       <c r="F8" s="3" t="s">
         <v>1266</v>
       </c>
-      <c r="G8" s="50" t="s">
+      <c r="G8" s="38" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="18" t="s">
         <v>1275</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>1288</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -10761,15 +10709,15 @@
       <c r="F9" s="3" t="s">
         <v>1266</v>
       </c>
-      <c r="G9" s="50" t="s">
+      <c r="G9" s="38" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="18" t="s">
         <v>1276</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="44" t="s">
         <v>1289</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -10781,15 +10729,15 @@
       <c r="F10" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="G10" s="50" t="s">
+      <c r="G10" s="38" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="18" t="s">
         <v>1277</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="44" t="s">
         <v>1290</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -10801,15 +10749,15 @@
       <c r="F11" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="G11" s="50" t="s">
+      <c r="G11" s="38" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="18" t="s">
         <v>1278</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="44" t="s">
         <v>1291</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -10821,15 +10769,15 @@
       <c r="F12" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="G12" s="50" t="s">
+      <c r="G12" s="38" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="18" t="s">
         <v>1279</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="44" t="s">
         <v>1292</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -10841,15 +10789,15 @@
       <c r="F13" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="G13" s="50" t="s">
+      <c r="G13" s="38" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="18" t="s">
         <v>1280</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="44" t="s">
         <v>1293</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -10861,15 +10809,15 @@
       <c r="F14" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="G14" s="50" t="s">
+      <c r="G14" s="38" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="18" t="s">
         <v>1281</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="44" t="s">
         <v>1294</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -10881,7 +10829,7 @@
       <c r="F15" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="G15" s="50" t="s">
+      <c r="G15" s="38" t="s">
         <v>264</v>
       </c>
     </row>
@@ -10904,30 +10852,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="18" t="s">
         <v>1315</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="44" t="s">
         <v>1339</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -10944,10 +10892,10 @@
       </c>
     </row>
     <row r="4" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="18" t="s">
         <v>1316</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>1340</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -10964,10 +10912,10 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>1317</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>1341</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -10984,10 +10932,10 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="18" t="s">
         <v>1318</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>1342</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -11004,10 +10952,10 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="18" t="s">
         <v>1319</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>1343</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -11024,10 +10972,10 @@
       </c>
     </row>
     <row r="8" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="18" t="s">
         <v>1320</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>1344</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -11044,10 +10992,10 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="18" t="s">
         <v>1321</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>1345</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -11064,10 +11012,10 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="18" t="s">
         <v>1322</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="44" t="s">
         <v>1346</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -11084,10 +11032,10 @@
       </c>
     </row>
     <row r="11" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="18" t="s">
         <v>1323</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="44" t="s">
         <v>1347</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -11104,10 +11052,10 @@
       </c>
     </row>
     <row r="12" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="18" t="s">
         <v>1324</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="44" t="s">
         <v>1348</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -11119,15 +11067,15 @@
       <c r="F12" s="3" t="s">
         <v>1310</v>
       </c>
-      <c r="G12" s="50" t="s">
+      <c r="G12" s="38" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="18" t="s">
         <v>1325</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="44" t="s">
         <v>1349</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -11139,15 +11087,15 @@
       <c r="F13" s="3" t="s">
         <v>1310</v>
       </c>
-      <c r="G13" s="50" t="s">
+      <c r="G13" s="38" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="18" t="s">
         <v>1326</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="44" t="s">
         <v>1350</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -11159,15 +11107,15 @@
       <c r="F14" s="3" t="s">
         <v>1310</v>
       </c>
-      <c r="G14" s="50" t="s">
+      <c r="G14" s="38" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="18" t="s">
         <v>1327</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="44" t="s">
         <v>1351</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -11179,15 +11127,15 @@
       <c r="F15" s="3" t="s">
         <v>1310</v>
       </c>
-      <c r="G15" s="50" t="s">
+      <c r="G15" s="38" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="18" t="s">
         <v>1328</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="44" t="s">
         <v>1352</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -11199,207 +11147,207 @@
       <c r="F16" s="3" t="s">
         <v>1310</v>
       </c>
-      <c r="G16" s="50" t="s">
+      <c r="G16" s="38" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="18" t="s">
         <v>1329</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="44" t="s">
         <v>1353</v>
       </c>
-      <c r="D17" s="51" t="s">
+      <c r="D17" s="39" t="s">
         <v>1380</v>
       </c>
-      <c r="E17" s="52" t="s">
+      <c r="E17" s="40" t="s">
         <v>1311</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="39" t="s">
         <v>1312</v>
       </c>
-      <c r="G17" s="50" t="s">
+      <c r="G17" s="38" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="18" t="s">
         <v>1330</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="44" t="s">
         <v>1354</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="39" t="s">
         <v>1380</v>
       </c>
-      <c r="E18" s="52" t="s">
+      <c r="E18" s="40" t="s">
         <v>1311</v>
       </c>
-      <c r="F18" s="51" t="s">
+      <c r="F18" s="39" t="s">
         <v>1312</v>
       </c>
-      <c r="G18" s="50" t="s">
+      <c r="G18" s="38" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="18" t="s">
         <v>1331</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="44" t="s">
         <v>1355</v>
       </c>
-      <c r="D19" s="51" t="s">
+      <c r="D19" s="39" t="s">
         <v>1380</v>
       </c>
-      <c r="E19" s="52" t="s">
+      <c r="E19" s="40" t="s">
         <v>1311</v>
       </c>
-      <c r="F19" s="51" t="s">
+      <c r="F19" s="39" t="s">
         <v>1312</v>
       </c>
-      <c r="G19" s="50" t="s">
+      <c r="G19" s="38" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="18" t="s">
         <v>1332</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="44" t="s">
         <v>1356</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="39" t="s">
         <v>1380</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="40" t="s">
         <v>1311</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="39" t="s">
         <v>1312</v>
       </c>
-      <c r="G20" s="50" t="s">
+      <c r="G20" s="38" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="44" t="s">
         <v>1357</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="39" t="s">
         <v>1380</v>
       </c>
-      <c r="E21" s="52" t="s">
+      <c r="E21" s="40" t="s">
         <v>1311</v>
       </c>
-      <c r="F21" s="51" t="s">
+      <c r="F21" s="39" t="s">
         <v>1312</v>
       </c>
-      <c r="G21" s="50" t="s">
+      <c r="G21" s="38" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="18" t="s">
         <v>1334</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="44" t="s">
         <v>1358</v>
       </c>
-      <c r="D22" s="51" t="s">
+      <c r="D22" s="39" t="s">
         <v>1380</v>
       </c>
-      <c r="E22" s="52" t="s">
+      <c r="E22" s="40" t="s">
         <v>1311</v>
       </c>
-      <c r="F22" s="51" t="s">
+      <c r="F22" s="39" t="s">
         <v>1312</v>
       </c>
-      <c r="G22" s="50" t="s">
+      <c r="G22" s="38" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="18" t="s">
         <v>1335</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="44" t="s">
         <v>1359</v>
       </c>
-      <c r="D23" s="51" t="s">
+      <c r="D23" s="39" t="s">
         <v>1380</v>
       </c>
-      <c r="E23" s="52" t="s">
+      <c r="E23" s="40" t="s">
         <v>1311</v>
       </c>
-      <c r="F23" s="51" t="s">
+      <c r="F23" s="39" t="s">
         <v>1312</v>
       </c>
-      <c r="G23" s="50" t="s">
+      <c r="G23" s="38" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="18" t="s">
         <v>1336</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>1360</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="D24" s="40" t="s">
         <v>1363</v>
       </c>
-      <c r="E24" s="52" t="s">
+      <c r="E24" s="40" t="s">
         <v>1313</v>
       </c>
-      <c r="F24" s="51" t="s">
+      <c r="F24" s="39" t="s">
         <v>1314</v>
       </c>
-      <c r="G24" s="50" t="s">
+      <c r="G24" s="38" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="18" t="s">
         <v>1337</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>1361</v>
       </c>
-      <c r="D25" s="52" t="s">
+      <c r="D25" s="40" t="s">
         <v>1364</v>
       </c>
-      <c r="E25" s="52" t="s">
+      <c r="E25" s="40" t="s">
         <v>1313</v>
       </c>
-      <c r="F25" s="51" t="s">
+      <c r="F25" s="39" t="s">
         <v>1314</v>
       </c>
-      <c r="G25" s="50" t="s">
+      <c r="G25" s="38" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="18" t="s">
         <v>1338</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>1362</v>
       </c>
-      <c r="D26" s="52" t="s">
+      <c r="D26" s="40" t="s">
         <v>1365</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="40" t="s">
         <v>1313</v>
       </c>
-      <c r="F26" s="51" t="s">
+      <c r="F26" s="39" t="s">
         <v>1314</v>
       </c>
-      <c r="G26" s="50" t="s">
+      <c r="G26" s="38" t="s">
         <v>272</v>
       </c>
     </row>
@@ -11418,34 +11366,34 @@
     <col min="4" max="4" width="59.5703125" customWidth="1"/>
     <col min="5" max="5" width="48.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="59.5703125" customWidth="1"/>
-    <col min="7" max="7" width="54.5703125" style="28" customWidth="1"/>
+    <col min="7" max="7" width="54.5703125" style="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="18" t="s">
         <v>1390</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="44" t="s">
         <v>1395</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -11462,10 +11410,10 @@
       </c>
     </row>
     <row r="4" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="18" t="s">
         <v>1391</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>1396</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -11482,10 +11430,10 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>1392</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>1397</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -11502,10 +11450,10 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="18" t="s">
         <v>1393</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>1398</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -11522,10 +11470,10 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="18" t="s">
         <v>1394</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>1399</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -11560,38 +11508,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="63" t="s">
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="59" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="60"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="69"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="64"/>
       <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
@@ -11607,13 +11555,13 @@
       <c r="K3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="66"/>
+      <c r="L3" s="61"/>
     </row>
     <row r="4" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>548</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -11648,7 +11596,7 @@
       <c r="B5" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>549</v>
       </c>
       <c r="D5" s="7" t="s">
@@ -11683,7 +11631,7 @@
       <c r="B6" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>550</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -11718,7 +11666,7 @@
       <c r="B7" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>551</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -11753,7 +11701,7 @@
       <c r="B8" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>552</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -11788,10 +11736,10 @@
       <c r="B9" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>553</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="39" t="s">
         <v>614</v>
       </c>
       <c r="E9" s="7" t="s">
@@ -11823,10 +11771,10 @@
       <c r="B10" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="44" t="s">
         <v>554</v>
       </c>
-      <c r="D10" s="57" t="s">
+      <c r="D10" s="39" t="s">
         <v>616</v>
       </c>
       <c r="E10" s="7" t="s">
@@ -11858,10 +11806,10 @@
       <c r="B11" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="44" t="s">
         <v>555</v>
       </c>
-      <c r="D11" s="57" t="s">
+      <c r="D11" s="39" t="s">
         <v>615</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -11893,10 +11841,10 @@
       <c r="B12" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="44" t="s">
         <v>556</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="D12" s="43" t="s">
         <v>605</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -11928,10 +11876,10 @@
       <c r="B13" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="44" t="s">
         <v>557</v>
       </c>
-      <c r="D13" s="56" t="s">
+      <c r="D13" s="43" t="s">
         <v>603</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -11963,7 +11911,7 @@
       <c r="B14" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="44" t="s">
         <v>558</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -11998,7 +11946,7 @@
       <c r="B15" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="44" t="s">
         <v>559</v>
       </c>
       <c r="D15" s="7" t="s">
@@ -12033,7 +11981,7 @@
       <c r="B16" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="44" t="s">
         <v>560</v>
       </c>
       <c r="D16" s="7" t="s">
@@ -12068,7 +12016,7 @@
       <c r="B17" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="44" t="s">
         <v>561</v>
       </c>
       <c r="D17" s="7" t="s">
@@ -12103,7 +12051,7 @@
       <c r="B18" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="44" t="s">
         <v>562</v>
       </c>
       <c r="D18" s="7" t="s">
@@ -12138,7 +12086,7 @@
       <c r="B19" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="44" t="s">
         <v>563</v>
       </c>
       <c r="D19" s="7" t="s">
@@ -12173,7 +12121,7 @@
       <c r="B20" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="44" t="s">
         <v>564</v>
       </c>
       <c r="D20" s="7" t="s">
@@ -12208,7 +12156,7 @@
       <c r="B21" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="44" t="s">
         <v>565</v>
       </c>
       <c r="D21" s="7" t="s">
@@ -12243,7 +12191,7 @@
       <c r="B22" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="44" t="s">
         <v>566</v>
       </c>
       <c r="D22" s="7" t="s">
@@ -12278,7 +12226,7 @@
       <c r="B23" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="44" t="s">
         <v>567</v>
       </c>
       <c r="D23" s="7" t="s">
@@ -12313,7 +12261,7 @@
       <c r="B24" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="44" t="s">
         <v>568</v>
       </c>
       <c r="D24" s="7" t="s">
@@ -12348,7 +12296,7 @@
       <c r="B25" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="44" t="s">
         <v>569</v>
       </c>
       <c r="D25" s="7" t="s">
@@ -12383,7 +12331,7 @@
       <c r="B26" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="44" t="s">
         <v>570</v>
       </c>
       <c r="D26" s="7" t="s">
@@ -12418,10 +12366,10 @@
       <c r="B27" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="44" t="s">
         <v>571</v>
       </c>
-      <c r="D27" s="56" t="s">
+      <c r="D27" s="43" t="s">
         <v>582</v>
       </c>
       <c r="E27" s="7" t="s">
@@ -12453,7 +12401,7 @@
       <c r="B28" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="44" t="s">
         <v>572</v>
       </c>
       <c r="D28" s="7" t="s">
@@ -12488,7 +12436,7 @@
       <c r="B29" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" s="44" t="s">
         <v>573</v>
       </c>
       <c r="D29" s="7" t="s">
@@ -12537,7 +12485,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="B3:G4"/>
+  <dimension ref="B2:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.42578125" customWidth="1"/>
@@ -12546,46 +12494,47 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
     <row r="3" spans="2:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>174</v>
-      </c>
-      <c r="E3" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" s="54" t="s">
-        <v>295</v>
-      </c>
-      <c r="G3" s="47" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
+      <c r="B3" s="22" t="s">
         <v>1412</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C3" s="22" t="s">
         <v>1411</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D3" s="23" t="s">
         <v>1410</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>1408</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>1409</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G3" s="19" t="s">
         <v>276</v>
       </c>
     </row>
+    <row r="4" spans="2:7" ht="150" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12604,39 +12553,39 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="G2" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="37" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="144.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="18" t="s">
         <v>1415</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="22" t="s">
         <v>1417</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="23" t="s">
         <v>279</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -12656,13 +12605,13 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="18" t="s">
         <v>1416</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="22" t="s">
         <v>1418</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="23" t="s">
         <v>285</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -12674,7 +12623,7 @@
       <c r="G4" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="H4" s="53" t="s">
+      <c r="H4" s="41" t="s">
         <v>283</v>
       </c>
       <c r="I4" s="19" t="s">
@@ -12701,45 +12650,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="57" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="93" t="s">
+      <c r="F2" s="82" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="95" t="s">
+      <c r="G2" s="80" t="s">
         <v>295</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="59" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="60"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="84"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="22" t="s">
         <v>1431</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="22" t="s">
         <v>1424</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="23" t="s">
         <v>1433</v>
       </c>
       <c r="E4" s="19" t="s">
@@ -12751,7 +12700,7 @@
       <c r="G4" s="3" t="s">
         <v>1428</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="23" t="s">
         <v>290</v>
       </c>
     </row>
@@ -12762,10 +12711,10 @@
       <c r="C5" s="2" t="s">
         <v>1425</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="27" t="s">
         <v>1434</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="28" t="s">
         <v>288</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -12774,18 +12723,18 @@
       <c r="G5" s="3" t="s">
         <v>1437</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="27" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>1431</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>1426</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="23" t="s">
         <v>1435</v>
       </c>
       <c r="E6" s="19" t="s">
@@ -12797,7 +12746,7 @@
       <c r="G6" s="3" t="s">
         <v>1429</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="23" t="s">
         <v>290</v>
       </c>
     </row>
@@ -12808,10 +12757,10 @@
       <c r="C7" s="4" t="s">
         <v>1427</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="27" t="s">
         <v>1436</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="28" t="s">
         <v>288</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -12820,7 +12769,7 @@
       <c r="G7" s="3" t="s">
         <v>1430</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="27" t="s">
         <v>289</v>
       </c>
     </row>
@@ -12852,38 +12801,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="63" t="s">
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="59" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="60"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="69"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="64"/>
       <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
@@ -12899,13 +12848,13 @@
       <c r="K3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="70"/>
+      <c r="L3" s="65"/>
     </row>
     <row r="4" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>618</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -12940,7 +12889,7 @@
       <c r="B5" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>619</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -12975,7 +12924,7 @@
       <c r="B6" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>620</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -13010,7 +12959,7 @@
       <c r="B7" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>621</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -13045,7 +12994,7 @@
       <c r="B8" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>622</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -13080,7 +13029,7 @@
       <c r="B9" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>623</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -13131,44 +13080,44 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="52.140625" style="88" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.140625" style="47" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="59" customWidth="1"/>
     <col min="7" max="9" width="25.7109375" customWidth="1"/>
     <col min="10" max="10" width="29.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="68" t="s">
+      <c r="G2" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="H2" s="65" t="s">
+      <c r="H2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="2:10" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="60"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
@@ -13183,7 +13132,7 @@
       <c r="B4" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="46" t="s">
         <v>657</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -13212,7 +13161,7 @@
       <c r="B5" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="C5" s="86" t="s">
+      <c r="C5" s="46" t="s">
         <v>658</v>
       </c>
       <c r="D5" s="7" t="s">
@@ -13241,7 +13190,7 @@
       <c r="B6" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C6" s="46" t="s">
         <v>659</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -13270,7 +13219,7 @@
       <c r="B7" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="46" t="s">
         <v>660</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -13299,7 +13248,7 @@
       <c r="B8" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="46" t="s">
         <v>661</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -13328,7 +13277,7 @@
       <c r="B9" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="46" t="s">
         <v>662</v>
       </c>
       <c r="D9" s="7" t="s">
@@ -13357,7 +13306,7 @@
       <c r="B10" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C10" s="86" t="s">
+      <c r="C10" s="46" t="s">
         <v>666</v>
       </c>
       <c r="D10" s="7" t="s">
@@ -13386,7 +13335,7 @@
       <c r="B11" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="C11" s="86" t="s">
+      <c r="C11" s="46" t="s">
         <v>663</v>
       </c>
       <c r="D11" s="7" t="s">
@@ -13415,7 +13364,7 @@
       <c r="B12" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="C12" s="86" t="s">
+      <c r="C12" s="46" t="s">
         <v>664</v>
       </c>
       <c r="D12" s="7" t="s">
@@ -13444,7 +13393,7 @@
       <c r="B13" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="46" t="s">
         <v>665</v>
       </c>
       <c r="D13" s="7" t="s">
@@ -13496,32 +13445,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="65"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="2:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="69"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="64"/>
       <c r="G3" s="20" t="s">
         <v>5</v>
       </c>
@@ -13533,7 +13482,7 @@
       <c r="B4" s="18" t="s">
         <v>691</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>686</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -13556,7 +13505,7 @@
       <c r="B5" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>687</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -13579,7 +13528,7 @@
       <c r="B6" s="18" t="s">
         <v>693</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>688</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -13602,7 +13551,7 @@
       <c r="B7" s="18" t="s">
         <v>694</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>689</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -13625,7 +13574,7 @@
       <c r="B8" s="18" t="s">
         <v>695</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>690</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -13670,32 +13619,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="65"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="2:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="60"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="69"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="64"/>
       <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
@@ -13704,10 +13653,10 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="18" t="s">
         <v>713</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="46" t="s">
         <v>719</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -13727,10 +13676,10 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>714</v>
       </c>
-      <c r="C5" s="86" t="s">
+      <c r="C5" s="46" t="s">
         <v>720</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -13750,10 +13699,10 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C6" s="46" t="s">
         <v>721</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -13773,10 +13722,10 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="18" t="s">
         <v>716</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="46" t="s">
         <v>722</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -13796,10 +13745,10 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="18" t="s">
         <v>717</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="46" t="s">
         <v>723</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -13819,10 +13768,10 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="18" t="s">
         <v>718</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="46" t="s">
         <v>724</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -13867,202 +13816,202 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="74" t="s">
+      <c r="G2" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="75"/>
+      <c r="H2" s="70"/>
     </row>
     <row r="3" spans="2:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="60"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="77"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="72"/>
     </row>
     <row r="4" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>747</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="42" t="s">
         <v>732</v>
       </c>
-      <c r="F4" s="55" t="s">
+      <c r="F4" s="42" t="s">
         <v>758</v>
       </c>
-      <c r="G4" s="72" t="s">
+      <c r="G4" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="H4" s="73"/>
+      <c r="H4" s="68"/>
     </row>
     <row r="5" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>748</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="42" t="s">
         <v>733</v>
       </c>
-      <c r="F5" s="55" t="s">
+      <c r="F5" s="42" t="s">
         <v>757</v>
       </c>
-      <c r="G5" s="72" t="s">
+      <c r="G5" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="H5" s="73"/>
+      <c r="H5" s="68"/>
     </row>
     <row r="6" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>741</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>749</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="42" t="s">
         <v>734</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="42" t="s">
         <v>760</v>
       </c>
-      <c r="G6" s="72" t="s">
+      <c r="G6" s="67" t="s">
         <v>142</v>
       </c>
-      <c r="H6" s="78"/>
+      <c r="H6" s="73"/>
     </row>
     <row r="7" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>750</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="E7" s="55" t="s">
+      <c r="E7" s="42" t="s">
         <v>735</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F7" s="42" t="s">
         <v>762</v>
       </c>
-      <c r="G7" s="72" t="s">
+      <c r="G7" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="H7" s="73"/>
+      <c r="H7" s="68"/>
     </row>
     <row r="8" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>751</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>763</v>
       </c>
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="45" t="s">
         <v>736</v>
       </c>
-      <c r="F8" s="85" t="s">
+      <c r="F8" s="45" t="s">
         <v>764</v>
       </c>
-      <c r="G8" s="72" t="s">
+      <c r="G8" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="H8" s="73"/>
+      <c r="H8" s="68"/>
     </row>
     <row r="9" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>752</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="E9" s="55" t="s">
+      <c r="E9" s="42" t="s">
         <v>737</v>
       </c>
-      <c r="F9" s="55" t="s">
+      <c r="F9" s="42" t="s">
         <v>766</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="H9" s="73"/>
+      <c r="H9" s="68"/>
     </row>
     <row r="10" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="44" t="s">
         <v>753</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="E10" s="55" t="s">
+      <c r="E10" s="42" t="s">
         <v>738</v>
       </c>
-      <c r="F10" s="55" t="s">
+      <c r="F10" s="42" t="s">
         <v>768</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="H10" s="73"/>
+      <c r="H10" s="68"/>
     </row>
     <row r="11" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="44" t="s">
         <v>754</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>769</v>
       </c>
-      <c r="E11" s="55" t="s">
+      <c r="E11" s="42" t="s">
         <v>739</v>
       </c>
-      <c r="F11" s="55" t="s">
+      <c r="F11" s="42" t="s">
         <v>770</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="H11" s="73"/>
+      <c r="H11" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -14099,32 +14048,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="65"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="2:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="69"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="64"/>
       <c r="G3" s="20" t="s">
         <v>5</v>
       </c>
@@ -14136,10 +14085,10 @@
       <c r="B4" s="18" t="s">
         <v>794</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>815</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="39" t="s">
         <v>836</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -14159,10 +14108,10 @@
       <c r="B5" s="18" t="s">
         <v>795</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>816</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="39" t="s">
         <v>838</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -14182,10 +14131,10 @@
       <c r="B6" s="18" t="s">
         <v>796</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>817</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="39" t="s">
         <v>840</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -14205,10 +14154,10 @@
       <c r="B7" s="18" t="s">
         <v>797</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="39" t="s">
         <v>842</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -14228,10 +14177,10 @@
       <c r="B8" s="18" t="s">
         <v>798</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>819</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="39" t="s">
         <v>844</v>
       </c>
       <c r="E8" s="7" t="s">
@@ -14251,10 +14200,10 @@
       <c r="B9" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>820</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="39" t="s">
         <v>845</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -14274,10 +14223,10 @@
       <c r="B10" s="18" t="s">
         <v>800</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="39" t="s">
         <v>847</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -14297,10 +14246,10 @@
       <c r="B11" s="18" t="s">
         <v>801</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="44" t="s">
         <v>822</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="39" t="s">
         <v>848</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -14309,7 +14258,7 @@
       <c r="F11" s="7" t="s">
         <v>780</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="11" t="s">
         <v>150</v>
       </c>
       <c r="H11" s="19" t="s">
@@ -14320,10 +14269,10 @@
       <c r="B12" s="18" t="s">
         <v>802</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="44" t="s">
         <v>823</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="39" t="s">
         <v>849</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -14332,7 +14281,7 @@
       <c r="F12" s="7" t="s">
         <v>850</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="11" t="s">
         <v>150</v>
       </c>
       <c r="H12" s="19" t="s">
@@ -14343,10 +14292,10 @@
       <c r="B13" s="18" t="s">
         <v>803</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="44" t="s">
         <v>824</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="39" t="s">
         <v>851</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -14355,10 +14304,10 @@
       <c r="F13" s="7" t="s">
         <v>852</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="22" t="s">
         <v>12</v>
       </c>
     </row>
@@ -14366,10 +14315,10 @@
       <c r="B14" s="18" t="s">
         <v>804</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="44" t="s">
         <v>825</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="39" t="s">
         <v>853</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -14378,10 +14327,10 @@
       <c r="F14" s="7" t="s">
         <v>854</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="G14" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="H14" s="22" t="s">
         <v>12</v>
       </c>
     </row>
@@ -14389,10 +14338,10 @@
       <c r="B15" s="18" t="s">
         <v>805</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="44" t="s">
         <v>826</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="39" t="s">
         <v>855</v>
       </c>
       <c r="E15" s="7" t="s">
@@ -14401,7 +14350,7 @@
       <c r="F15" s="7" t="s">
         <v>856</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="11" t="s">
         <v>150</v>
       </c>
       <c r="H15" s="19" t="s">
@@ -14412,10 +14361,10 @@
       <c r="B16" s="18" t="s">
         <v>806</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="44" t="s">
         <v>827</v>
       </c>
-      <c r="D16" s="51" t="s">
+      <c r="D16" s="39" t="s">
         <v>857</v>
       </c>
       <c r="E16" s="7" t="s">
@@ -14424,10 +14373,10 @@
       <c r="F16" s="7" t="s">
         <v>858</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="22" t="s">
         <v>158</v>
       </c>
     </row>
@@ -14435,10 +14384,10 @@
       <c r="B17" s="18" t="s">
         <v>807</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="44" t="s">
         <v>828</v>
       </c>
-      <c r="D17" s="51" t="s">
+      <c r="D17" s="39" t="s">
         <v>859</v>
       </c>
       <c r="E17" s="7" t="s">
@@ -14447,7 +14396,7 @@
       <c r="F17" s="7" t="s">
         <v>860</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="11" t="s">
         <v>133</v>
       </c>
       <c r="H17" s="19" t="s">
@@ -14458,34 +14407,34 @@
       <c r="B18" s="18" t="s">
         <v>808</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="44" t="s">
         <v>829</v>
       </c>
-      <c r="D18" s="89" t="s">
+      <c r="D18" s="48" t="s">
         <v>861</v>
       </c>
-      <c r="E18" s="89" t="s">
+      <c r="E18" s="48" t="s">
         <v>785</v>
       </c>
-      <c r="F18" s="89" t="s">
+      <c r="F18" s="48" t="s">
         <v>862</v>
       </c>
-      <c r="G18" s="90" t="s">
+      <c r="G18" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="H18" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="I18" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="J18" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="91" t="s">
+      <c r="H18" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18" s="50" t="s">
         <v>792</v>
       </c>
-      <c r="L18" s="92" t="s">
+      <c r="L18" s="51" t="s">
         <v>793</v>
       </c>
     </row>
@@ -14493,10 +14442,10 @@
       <c r="B19" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="44" t="s">
         <v>830</v>
       </c>
-      <c r="D19" s="51" t="s">
+      <c r="D19" s="39" t="s">
         <v>863</v>
       </c>
       <c r="E19" s="7" t="s">
@@ -14505,7 +14454,7 @@
       <c r="F19" s="7" t="s">
         <v>864</v>
       </c>
-      <c r="G19" s="23" t="s">
+      <c r="G19" s="11" t="s">
         <v>150</v>
       </c>
       <c r="H19" s="5" t="s">
@@ -14516,10 +14465,10 @@
       <c r="B20" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="44" t="s">
         <v>831</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="39" t="s">
         <v>865</v>
       </c>
       <c r="E20" s="7" t="s">
@@ -14528,7 +14477,7 @@
       <c r="F20" s="7" t="s">
         <v>866</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="11" t="s">
         <v>150</v>
       </c>
       <c r="H20" s="5" t="s">
@@ -14539,10 +14488,10 @@
       <c r="B21" s="18" t="s">
         <v>811</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="44" t="s">
         <v>832</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="39" t="s">
         <v>867</v>
       </c>
       <c r="E21" s="7" t="s">
@@ -14551,7 +14500,7 @@
       <c r="F21" s="7" t="s">
         <v>868</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="11" t="s">
         <v>150</v>
       </c>
       <c r="H21" s="19" t="s">
@@ -14562,10 +14511,10 @@
       <c r="B22" s="18" t="s">
         <v>812</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="44" t="s">
         <v>833</v>
       </c>
-      <c r="D22" s="51" t="s">
+      <c r="D22" s="39" t="s">
         <v>869</v>
       </c>
       <c r="E22" s="7" t="s">
@@ -14574,7 +14523,7 @@
       <c r="F22" s="7" t="s">
         <v>870</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="11" t="s">
         <v>163</v>
       </c>
       <c r="H22" s="19" t="s">
@@ -14585,10 +14534,10 @@
       <c r="B23" s="18" t="s">
         <v>813</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="44" t="s">
         <v>834</v>
       </c>
-      <c r="D23" s="51" t="s">
+      <c r="D23" s="39" t="s">
         <v>871</v>
       </c>
       <c r="E23" s="7" t="s">
@@ -14597,7 +14546,7 @@
       <c r="F23" s="7" t="s">
         <v>872</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="11" t="s">
         <v>165</v>
       </c>
       <c r="H23" s="5" t="s">
@@ -14608,10 +14557,10 @@
       <c r="B24" s="18" t="s">
         <v>814</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="44" t="s">
         <v>835</v>
       </c>
-      <c r="D24" s="51" t="s">
+      <c r="D24" s="39" t="s">
         <v>873</v>
       </c>
       <c r="E24" s="7" t="s">
@@ -14620,10 +14569,10 @@
       <c r="F24" s="7" t="s">
         <v>874</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H24" s="11" t="s">
         <v>168</v>
       </c>
     </row>
@@ -14662,10 +14611,10 @@
       <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="17" t="s">
         <v>295</v>
       </c>
       <c r="G2" s="17" t="s">
@@ -14676,7 +14625,7 @@
       <c r="B3" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="44" t="s">
         <v>877</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -14696,7 +14645,7 @@
       <c r="B4" s="4" t="s">
         <v>892</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>878</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -14716,7 +14665,7 @@
       <c r="B5" s="4" t="s">
         <v>893</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="44" t="s">
         <v>879</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -14736,7 +14685,7 @@
       <c r="B6" s="4" t="s">
         <v>894</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="44" t="s">
         <v>880</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -14756,7 +14705,7 @@
       <c r="B7" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="44" t="s">
         <v>881</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -14776,7 +14725,7 @@
       <c r="B8" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="44" t="s">
         <v>882</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -14796,7 +14745,7 @@
       <c r="B9" s="4" t="s">
         <v>897</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="44" t="s">
         <v>883</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -14816,7 +14765,7 @@
       <c r="B10" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="44" t="s">
         <v>884</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -14836,7 +14785,7 @@
       <c r="B11" s="4" t="s">
         <v>899</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="44" t="s">
         <v>885</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -14856,7 +14805,7 @@
       <c r="B12" s="4" t="s">
         <v>900</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="44" t="s">
         <v>886</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -14876,7 +14825,7 @@
       <c r="B13" s="4" t="s">
         <v>901</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="44" t="s">
         <v>887</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -14896,7 +14845,7 @@
       <c r="B14" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="44" t="s">
         <v>888</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -14916,7 +14865,7 @@
       <c r="B15" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="44" t="s">
         <v>889</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -14936,7 +14885,7 @@
       <c r="B16" s="4" t="s">
         <v>904</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="44" t="s">
         <v>890</v>
       </c>
       <c r="D16" s="3" t="s">
